--- a/public/format_file_excel_import/kepala_keluarga_pekerjaan.xlsx
+++ b/public/format_file_excel_import/kepala_keluarga_pekerjaan.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ariesyarwani/Documents/format excel import/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Rumah data 2.0\public\format_file_excel_import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09278BF0-C8CB-8849-85B4-0BADE79A954F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5386445C-53E9-47CA-9539-E6BB544BE374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1240" windowWidth="27640" windowHeight="16760" xr2:uid="{9F0C61F8-DFF9-114A-8F8C-91ECB181F7CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9F0C61F8-DFF9-114A-8F8C-91ECB181F7CD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -485,30 +483,12 @@
     <t>perawat_p</t>
   </si>
   <si>
-    <t>apotek_l</t>
-  </si>
-  <si>
-    <t>apotek_p</t>
-  </si>
-  <si>
     <t>psikiater_psikolog_l</t>
   </si>
   <si>
     <t>psikiater_psikolog_p</t>
   </si>
   <si>
-    <t>penyiara_televisi_l</t>
-  </si>
-  <si>
-    <t>penyiara_televisi_p</t>
-  </si>
-  <si>
-    <t>penyiara_radio_l</t>
-  </si>
-  <si>
-    <t>penyiara_radio_p</t>
-  </si>
-  <si>
     <t>pelaut_l</t>
   </si>
   <si>
@@ -611,12 +591,6 @@
     <t>operator_p</t>
   </si>
   <si>
-    <t>pekerja_pengolahan_krajinan_l</t>
-  </si>
-  <si>
-    <t>pekerja_pengolahan_krajinan_p</t>
-  </si>
-  <si>
     <t>teknisi_l</t>
   </si>
   <si>
@@ -633,25 +607,43 @@
   </si>
   <si>
     <t>pekerjaan_lainnya_p</t>
+  </si>
+  <si>
+    <t>apoteker_l</t>
+  </si>
+  <si>
+    <t>apoteker_p</t>
+  </si>
+  <si>
+    <t>penyiar_televisi_l</t>
+  </si>
+  <si>
+    <t>penyiar_televisi_p</t>
+  </si>
+  <si>
+    <t>penyiar_radio_l</t>
+  </si>
+  <si>
+    <t>penyiar_radio_p</t>
+  </si>
+  <si>
+    <t>pekerja_pengolahan_kerajinan_l</t>
+  </si>
+  <si>
+    <t>pekerja_pengolahan_kerajinan_p</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Menlo"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -674,33 +666,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Menlo"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -714,208 +686,208 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6D6ED365-FED1-7447-8572-39D953C49024}" name="Table1" displayName="Table1" ref="A1:GQ2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:GQ2" xr:uid="{6D6ED365-FED1-7447-8572-39D953C49024}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{17421D9A-4891-40B5-A26A-C1CACFEAFF1B}" name="Table2" displayName="Table2" ref="A1:GQ2" insertRow="1" totalsRowShown="0">
+  <autoFilter ref="A1:GQ2" xr:uid="{17421D9A-4891-40B5-A26A-C1CACFEAFF1B}"/>
   <tableColumns count="199">
-    <tableColumn id="1" xr3:uid="{345D1603-B35C-1C46-9376-47E0FA657326}" name="kode_wilayah" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{08A23DFB-0653-4F40-9EF0-93692889FC50}" name="belum_tidak_bekerja_l"/>
-    <tableColumn id="3" xr3:uid="{729604AD-7B07-4A47-B6D9-EDF35222846D}" name="belum_tidak_bekerja_p"/>
-    <tableColumn id="4" xr3:uid="{32C6062E-6C13-534D-8037-72AE2940FAAD}" name="mengurus_rumah_tangga_l"/>
-    <tableColumn id="5" xr3:uid="{B75305B7-D0F0-CE4F-9225-1A82F0C9EF54}" name="mengurus_rumah_tangga_p"/>
-    <tableColumn id="6" xr3:uid="{EC55EC5E-EFB1-A442-806D-376D11E8C45C}" name="pelajar_mahasiswa_l"/>
-    <tableColumn id="7" xr3:uid="{7E230F2B-3CAC-CB49-96DA-94D081B0DA72}" name="pelajar_mahasiswa_p"/>
-    <tableColumn id="8" xr3:uid="{FE0E1856-8441-5B40-A80B-0900947C920D}" name="pensiunan_l"/>
-    <tableColumn id="9" xr3:uid="{C9F519F0-49AB-074E-9807-71603AB0781F}" name="pensiunan_p"/>
-    <tableColumn id="10" xr3:uid="{91ECB0A3-F47B-A04A-BD83-E3A7CE14B739}" name="pegawai_negeri_sipil_pns_l"/>
-    <tableColumn id="11" xr3:uid="{8EB953A4-F648-DC43-AA85-0E81A4354FFD}" name="pegawai_negeri_sipil_pns_p"/>
-    <tableColumn id="12" xr3:uid="{316B5C0C-42F8-9946-BE4A-6AF8548FDAA0}" name="tentara_nasional_indonesia_tni_l"/>
-    <tableColumn id="13" xr3:uid="{334B48B2-EC24-D048-8054-27E246325870}" name="tentara_nasional_indonesia_tni_p"/>
-    <tableColumn id="14" xr3:uid="{7F344855-B792-D343-A274-41E073B06E13}" name="kepolisian_ri_polri_l"/>
-    <tableColumn id="15" xr3:uid="{1147596F-6E61-EC4B-B3FD-E9C4F549EAB9}" name="kepolisian_ri_polri_p"/>
-    <tableColumn id="16" xr3:uid="{5C94C592-8F97-1848-B9E3-5DEA16CC4222}" name="perdagangan_l"/>
-    <tableColumn id="17" xr3:uid="{86D65816-715C-4A44-9544-31E76B52B75C}" name="perdagangan_p"/>
-    <tableColumn id="18" xr3:uid="{D36051DC-FDCA-BD48-952B-11CA70C066E0}" name="petani_pekebun_l"/>
-    <tableColumn id="19" xr3:uid="{016F6F3B-5BC1-1144-916E-6CE635C3685C}" name="petani_pekebun_p"/>
-    <tableColumn id="20" xr3:uid="{27DFEAAE-7E45-A74D-942A-616702ABEEA2}" name="peternak_l"/>
-    <tableColumn id="21" xr3:uid="{F45FEFAC-DEAA-9941-8425-41836CBF2286}" name="peternak_p"/>
-    <tableColumn id="22" xr3:uid="{503BD235-071B-4D47-B2C9-FE12DCFD7831}" name="nelayan_perikanan_l"/>
-    <tableColumn id="23" xr3:uid="{DF034B37-0F8C-6141-BD74-5FD523A6F132}" name="nelayan_perikanan_p"/>
-    <tableColumn id="24" xr3:uid="{328EF488-37A0-1349-B92B-E6F7C5C264ED}" name="industri_l"/>
-    <tableColumn id="25" xr3:uid="{70597D62-A639-9849-93FA-407ED2C089CC}" name="industri_p"/>
-    <tableColumn id="26" xr3:uid="{730D6106-74D1-6D40-8E48-E17739F57916}" name="konstruksi_l"/>
-    <tableColumn id="27" xr3:uid="{BAF70DF7-DD0B-BF43-A191-B4527C96B474}" name="konstruksi_p"/>
-    <tableColumn id="28" xr3:uid="{3D9D10AF-502F-2344-8637-D62B2F2DB000}" name="transportasi_l"/>
-    <tableColumn id="29" xr3:uid="{3F16261C-442B-1841-BC1D-07F77FD2A46D}" name="transportasi_p"/>
-    <tableColumn id="30" xr3:uid="{9FD38254-A89F-D74F-900B-B0A0AE75B97F}" name="karyawan_swasta_l"/>
-    <tableColumn id="31" xr3:uid="{4FE5B2DD-0B44-1743-8A88-3A0B7129867E}" name="karyawan_swasta_p"/>
-    <tableColumn id="32" xr3:uid="{8E61FD28-3976-B44C-BB7A-0AF530118917}" name="karyawan_bumn_l"/>
-    <tableColumn id="33" xr3:uid="{56F60104-4DC7-024E-9697-6696A77C0C41}" name="karyawan_bumn_p"/>
-    <tableColumn id="34" xr3:uid="{C6DD5E95-3219-7F4F-B155-8B6964D59C36}" name="karyawan_bumd_l"/>
-    <tableColumn id="35" xr3:uid="{100D2B0E-7399-C548-BBCD-6F1F3EF4E9FF}" name="karyawan_bumd_p"/>
-    <tableColumn id="36" xr3:uid="{81C3AF60-D883-334D-A77F-1E82ED8DC25D}" name="karyawan_honorer_l"/>
-    <tableColumn id="37" xr3:uid="{DB81FCB6-2388-824F-B1E0-F05821675EA2}" name="karyawan_honorer_p"/>
-    <tableColumn id="38" xr3:uid="{4767440A-0FA2-4243-8993-DCF3554B3290}" name="buruh_harian_lepas_l"/>
-    <tableColumn id="39" xr3:uid="{2B836085-69FB-074A-9324-BEE939727A15}" name="buruh_harian_lepas_p"/>
-    <tableColumn id="40" xr3:uid="{828487EE-3FDB-F942-982A-53C4A9BAF19C}" name="buruh_tani_perkebunan_l"/>
-    <tableColumn id="41" xr3:uid="{6D5D0705-6793-CC4F-BCC5-1138EA577B45}" name="buruh_tani_perkebunan_p"/>
-    <tableColumn id="42" xr3:uid="{800F6780-0892-5643-ACF3-9719FC8A605B}" name="buruh_nelayan_perikanan_l"/>
-    <tableColumn id="43" xr3:uid="{B963F2E3-E78A-4647-AE5F-1CB25F49C5C0}" name="buruh_nelayan_perikanan_p"/>
-    <tableColumn id="44" xr3:uid="{84B204B1-0E97-8547-9B9E-38BD27DFF74D}" name="buruh_peternakan_l"/>
-    <tableColumn id="45" xr3:uid="{F4F0C204-AA49-6D4B-A019-6CF715C0FED9}" name="buruh_peternakan_p"/>
-    <tableColumn id="46" xr3:uid="{36D34262-7901-C249-B539-8E9995C7FC3E}" name="pembantu_rumah_tangga_l"/>
-    <tableColumn id="47" xr3:uid="{9D0FEC98-3204-8543-9C56-6A976F1D597A}" name="pembantu_rumah_tangga_p"/>
-    <tableColumn id="48" xr3:uid="{D34F8332-65C1-EB4F-B271-0B76A351A6D1}" name="tukang_cukur_l"/>
-    <tableColumn id="49" xr3:uid="{AADA3AAA-FAB4-3343-828B-DA702FA982B6}" name="tukang_cukur_p"/>
-    <tableColumn id="50" xr3:uid="{0A106C4B-AFF3-BB4F-A059-E4585C54976A}" name="tukang_listrik_l"/>
-    <tableColumn id="51" xr3:uid="{FFE482CA-AE60-CE43-8796-4035ACAD55E2}" name="tukang_listrik_p"/>
-    <tableColumn id="52" xr3:uid="{4436B657-7271-8A47-8203-1B11BE1E26C4}" name="tukang_batu_l"/>
-    <tableColumn id="53" xr3:uid="{FAACBF70-5CCC-8F41-9B6D-949D11EC7101}" name="tukang_batu_p"/>
-    <tableColumn id="54" xr3:uid="{233457B1-D3B8-A24C-89CC-CA5D483DDB1C}" name="tukang_kayu_l"/>
-    <tableColumn id="55" xr3:uid="{26E7A7C5-01E4-3C4D-A955-837BEB0A7231}" name="tukang_kayu_p"/>
-    <tableColumn id="56" xr3:uid="{077B1F83-A85C-934A-989A-4FF342D3F83C}" name="tukang_sol_sepatu_l"/>
-    <tableColumn id="57" xr3:uid="{BD85514D-C749-F44B-ACDE-556A1EFFED68}" name="tukang_sol_sepatu_p"/>
-    <tableColumn id="58" xr3:uid="{EEF110ED-EBE9-CF41-9A65-DB7B2326E5C5}" name="tukang_las_pandai_besi_l"/>
-    <tableColumn id="59" xr3:uid="{29E95FD8-E66F-6049-AB1E-71B93369F241}" name="tukang_las_pandai_besi_p"/>
-    <tableColumn id="60" xr3:uid="{F5296C22-C16E-AA47-A61E-3632930E5734}" name="tukang_jahit_l"/>
-    <tableColumn id="61" xr3:uid="{C4313964-D920-6941-BDCE-69E90EEBB899}" name="tukang_jahit_p"/>
-    <tableColumn id="62" xr3:uid="{546C61B4-FEFD-0F48-8350-1B588922844B}" name="tukang_gigi_l"/>
-    <tableColumn id="63" xr3:uid="{0FD5D6FD-C894-6545-9219-FE0C7C873E65}" name="tukang_gigi_p"/>
-    <tableColumn id="64" xr3:uid="{EB7B9EFF-6081-4343-995A-E3A5735D5CD2}" name="penata_rias_l"/>
-    <tableColumn id="65" xr3:uid="{1E9E1B25-F231-E645-8480-09E091320A3B}" name="penata_rias_p"/>
-    <tableColumn id="66" xr3:uid="{E1BF4901-398F-EB43-B961-2AEF6822EE77}" name="penata_busana_l"/>
-    <tableColumn id="67" xr3:uid="{B8434F96-83B8-F545-B9AC-EE6AB5E5D135}" name="penata_busana_p"/>
-    <tableColumn id="68" xr3:uid="{307998D1-2627-FE44-B390-8358269181C4}" name="penata_rambut_l"/>
-    <tableColumn id="69" xr3:uid="{6D1432D5-3A7C-7844-B4AD-F62F1413C6D7}" name="penata_rambut_p"/>
-    <tableColumn id="70" xr3:uid="{936A630F-1B17-4A45-846D-4D72F2FEFBC1}" name="mekanik_l"/>
-    <tableColumn id="71" xr3:uid="{7AEBDE20-1BEF-8A40-96FD-AB71CCE26302}" name="mekanik_p"/>
-    <tableColumn id="72" xr3:uid="{7D046F20-3FD9-4242-A1E9-338DA056FDBB}" name="seniman_l"/>
-    <tableColumn id="73" xr3:uid="{62FAB8E8-EBA4-B346-91DD-55150DD8A32F}" name="seniman_p"/>
-    <tableColumn id="74" xr3:uid="{38F98075-547C-D74D-8B2A-C52C0CAE6985}" name="tabib_l"/>
-    <tableColumn id="75" xr3:uid="{BCCFC73A-81FF-A34D-8A96-CA19886B455B}" name="tabib_p"/>
-    <tableColumn id="76" xr3:uid="{22995E2E-7218-F544-AE69-5DAB06BC19F1}" name="paraji_l"/>
-    <tableColumn id="77" xr3:uid="{FF59CE4E-7937-E144-8659-697055D9D6C1}" name="paraji_p"/>
-    <tableColumn id="78" xr3:uid="{0A42A034-1B4B-6A4C-8944-CB57792B735F}" name="perancang_busana_l"/>
-    <tableColumn id="79" xr3:uid="{9B30D26D-5AAD-B64B-9DFA-11394389E0FF}" name="perancang_busana_p"/>
-    <tableColumn id="80" xr3:uid="{644A9AA8-DC60-C547-8440-34244664C44C}" name="penterjemah_l"/>
-    <tableColumn id="81" xr3:uid="{076820DC-643E-0E45-B205-46B333C88F79}" name="penterjemah_p"/>
-    <tableColumn id="82" xr3:uid="{1444341C-6F4E-9C44-BEAB-D00D477EB8C2}" name="imam_masjid_l"/>
-    <tableColumn id="83" xr3:uid="{CD1D1531-E9BB-3748-BFC5-CF781C3DB243}" name="imam_masjid_p"/>
-    <tableColumn id="84" xr3:uid="{5E60C38F-9B6D-E642-ADE2-C992D0D24BB7}" name="pendeta_l"/>
-    <tableColumn id="85" xr3:uid="{5086872D-811B-0440-A7C8-D1EBC143BA21}" name="pendeta_p"/>
-    <tableColumn id="86" xr3:uid="{103EBD72-4086-BF46-A4B0-1B15F050AAA5}" name="pastor_l"/>
-    <tableColumn id="87" xr3:uid="{6B662080-DC13-E141-A908-F9745F748175}" name="pastor_p"/>
-    <tableColumn id="88" xr3:uid="{91CAB4E2-C909-C84C-9962-29D8F765A917}" name="wartawan_l"/>
-    <tableColumn id="89" xr3:uid="{39E14BE2-853D-9D4E-80D7-38E8ED548DFD}" name="wartawan_p"/>
-    <tableColumn id="90" xr3:uid="{3030DC6B-A8B5-A548-9375-E5A83B1ED399}" name="ustadz_mubaligh_l"/>
-    <tableColumn id="91" xr3:uid="{8AF94244-1648-194F-817A-CE9CDC00057D}" name="ustadz_mubaligh_p"/>
-    <tableColumn id="92" xr3:uid="{A560CA69-B48D-564F-82D6-A98BF30890B9}" name="juru_masak_l"/>
-    <tableColumn id="93" xr3:uid="{F4DE5675-12A9-7641-A186-BAF429A0D6DE}" name="juru_masak_p"/>
-    <tableColumn id="94" xr3:uid="{01BE6B0D-CB43-9946-86E1-F7BBF0CCAE18}" name="promotor_acara_l"/>
-    <tableColumn id="95" xr3:uid="{A0B72F08-729B-3A42-BDAE-07257628D737}" name="promotor_acara_p"/>
-    <tableColumn id="96" xr3:uid="{E1716CD6-26D7-B64C-B40E-1419CDA1E117}" name="anggota_dpr_ri_l"/>
-    <tableColumn id="97" xr3:uid="{2E1D13E0-5022-1F4F-92CB-884A84C2224F}" name="anggota_dpr_ri_p"/>
-    <tableColumn id="98" xr3:uid="{6B2B01F4-D733-8041-9D4A-328F5D7E3F6A}" name="anggota_dpd_ri_l"/>
-    <tableColumn id="99" xr3:uid="{DF03994B-9085-A24A-9894-C8379DD4BD34}" name="anggota_dpd_ri_p"/>
-    <tableColumn id="100" xr3:uid="{027D6B48-7286-BF40-B5FC-1734ADF84ED3}" name="anggota_bpk_l"/>
-    <tableColumn id="101" xr3:uid="{920CB12F-6BE0-EF4B-96A9-79284B89CCB8}" name="anggota_bpk_p"/>
-    <tableColumn id="102" xr3:uid="{0F32CD58-16DE-EB40-9139-7F6DC084AA09}" name="presiden_l"/>
-    <tableColumn id="103" xr3:uid="{CC71328B-D488-ED4D-BB21-1D70C5AF37F9}" name="presiden_p"/>
-    <tableColumn id="104" xr3:uid="{718B94FC-424E-B046-A879-C5FAF2FAA43C}" name="wakil_presiden_l"/>
-    <tableColumn id="105" xr3:uid="{0A586EB2-8DCB-514A-9FA9-86BAAC68C6F1}" name="wakil_presiden_p"/>
-    <tableColumn id="106" xr3:uid="{55FDCF4B-8082-1F4B-AF4A-D3CDDB75BE3D}" name="anggota_mahkamah_konstitusi_l"/>
-    <tableColumn id="107" xr3:uid="{9C49A19E-3D5F-974B-90B1-AE3D64F59746}" name="anggota_mahkamah_konstitusi_p"/>
-    <tableColumn id="108" xr3:uid="{3F92BAE8-E109-5240-ABD1-33BBD11D30EB}" name="anggota_kabinet_kementerian_l"/>
-    <tableColumn id="109" xr3:uid="{9EF841AE-281A-4B47-AA4C-8DD2DD3B349D}" name="anggota_kabinet_kementerian_p"/>
-    <tableColumn id="110" xr3:uid="{7EB3C06D-6874-CE41-9262-AEDFFEEE2820}" name="duta_besar_l"/>
-    <tableColumn id="111" xr3:uid="{C25D57BD-5B64-1C4E-B63F-87A5565C686E}" name="duta_besar _p"/>
-    <tableColumn id="112" xr3:uid="{C8E8B6F5-C168-B644-AF94-E4FE35533B02}" name="gubernur_l"/>
-    <tableColumn id="113" xr3:uid="{6A8943E1-1C05-4F40-9FC0-9C84527B8256}" name="gubernur_p"/>
-    <tableColumn id="114" xr3:uid="{B1C439DD-BBA8-074F-A6FB-21B6715D3E9A}" name="wakil_gubernur_l"/>
-    <tableColumn id="115" xr3:uid="{7EE83446-0343-B744-BD4C-EFFB982DC3CD}" name="wakil_gubernur_p"/>
-    <tableColumn id="116" xr3:uid="{3E93E570-A7DB-2642-B088-128F8FF3CBDB}" name="bupati_l"/>
-    <tableColumn id="117" xr3:uid="{4BC0505E-5114-6944-9DD9-E5800CF32B18}" name="bupati_p"/>
-    <tableColumn id="118" xr3:uid="{3558CB40-FD52-CA4B-A42C-7B66D5DAE1A0}" name="wakil_bupati_l"/>
-    <tableColumn id="119" xr3:uid="{1850346E-8B6D-F748-8B8B-D97B7873E3F1}" name="wakil_bupati_p"/>
-    <tableColumn id="120" xr3:uid="{54F30865-93E5-674E-AF62-8E040BA901D2}" name="walikota_l"/>
-    <tableColumn id="121" xr3:uid="{56B0FEC6-2A49-6545-A1D4-D923874FC202}" name="walikota_p"/>
-    <tableColumn id="122" xr3:uid="{EA7323BC-965B-F84B-91B4-F9FE0CF08AF1}" name="wakil_walikota_l"/>
-    <tableColumn id="123" xr3:uid="{C655FCD8-58D1-FF42-BA1D-6170CC38DF2A}" name="wakil_walikota_p"/>
-    <tableColumn id="124" xr3:uid="{C3B0E8B1-4079-0C46-A6E8-E5374A6CA448}" name="anggota_dprd_prop_l"/>
-    <tableColumn id="125" xr3:uid="{2F98FFBC-9363-E047-A08B-72C04D81E978}" name="anggota_dprd_prop_p"/>
-    <tableColumn id="126" xr3:uid="{F1057B54-452D-8F4D-BC9A-1969246D0F5D}" name="anggota_dprd_kab_kota_l"/>
-    <tableColumn id="127" xr3:uid="{5A692BF5-8CFA-094D-B501-B07BE80DE11C}" name="anggota_dprd_kab_kota_p"/>
-    <tableColumn id="128" xr3:uid="{6A3A6173-9D58-ED46-9ADB-D6993F628706}" name="dosen_l"/>
-    <tableColumn id="129" xr3:uid="{BF46A098-91A8-6446-9AF8-1C5235B31EDD}" name="dosen_p"/>
-    <tableColumn id="130" xr3:uid="{8D1D2E89-BD8A-3540-AED8-500BA7FFA51D}" name="guru_l"/>
-    <tableColumn id="131" xr3:uid="{9F099788-C3AD-B245-9FFB-BB70A570D43F}" name="guru_p"/>
-    <tableColumn id="132" xr3:uid="{BADBF9DE-B198-0944-9560-6890877CBD59}" name="pilot_l"/>
-    <tableColumn id="133" xr3:uid="{39CBC011-7D4F-F54E-BA9B-867D37B0F755}" name="pilot_p"/>
-    <tableColumn id="134" xr3:uid="{0895DA78-93B4-F246-9F81-B79CA2ED486C}" name="pengacara_l"/>
-    <tableColumn id="135" xr3:uid="{C8D090CE-46AD-F14C-9E7B-76D84EA5B318}" name="pengacara_p"/>
-    <tableColumn id="136" xr3:uid="{86A44457-8A66-324B-BD61-416EC52DF370}" name="notaris_l"/>
-    <tableColumn id="137" xr3:uid="{80956648-C59D-DB40-A565-7D07BD8FEACC}" name="notaris_p"/>
-    <tableColumn id="138" xr3:uid="{B92F8E66-B888-A241-B6F1-9D131B3E5EC5}" name="arsitek_l"/>
-    <tableColumn id="139" xr3:uid="{D348F470-3564-154B-B644-9959A83FDEA3}" name="arsitek_p"/>
-    <tableColumn id="140" xr3:uid="{22D0A0AF-5F53-724E-A205-A6473BDAC1A4}" name="akuntan_l"/>
-    <tableColumn id="141" xr3:uid="{4C41113F-21B2-694D-B657-3816576474C4}" name="akuntan_p"/>
-    <tableColumn id="142" xr3:uid="{815C51CE-483D-AE45-852D-CAE70784F0C3}" name="konsultan_l"/>
-    <tableColumn id="143" xr3:uid="{115F2950-47E2-8446-8598-26A4D65BCBFE}" name="konsultan_p"/>
-    <tableColumn id="144" xr3:uid="{3F83C760-7793-7949-9227-31B3450B20E0}" name="dokter_l"/>
-    <tableColumn id="145" xr3:uid="{A1A6F305-6FE0-7E47-AC5F-B9CF69632C9C}" name="dokter_p"/>
-    <tableColumn id="146" xr3:uid="{5836DF33-ED5B-1E4B-85EE-51175C7DB19B}" name="bidan_l"/>
-    <tableColumn id="147" xr3:uid="{0E154EF8-1134-8B44-AADB-D6338C758F7C}" name="bidan_p"/>
-    <tableColumn id="148" xr3:uid="{B170464D-64E9-F24C-9772-16D99F991E8C}" name="perawat_l"/>
-    <tableColumn id="149" xr3:uid="{0BE954E5-43F0-3C48-9763-98CCD9A253EC}" name="perawat_p"/>
-    <tableColumn id="150" xr3:uid="{3B8CD2A9-4DBE-4740-8988-DDCDC1B49277}" name="apotek_l"/>
-    <tableColumn id="151" xr3:uid="{55D2544B-4114-F644-BEEA-FB4FFD85A7DC}" name="apotek_p"/>
-    <tableColumn id="152" xr3:uid="{890B2171-31FF-5F44-A853-5EB031BEE5F1}" name="psikiater_psikolog_l"/>
-    <tableColumn id="153" xr3:uid="{997A8167-D7D9-3A4E-9BDD-A73359E5C116}" name="psikiater_psikolog_p"/>
-    <tableColumn id="154" xr3:uid="{167AC58A-3B3B-AD4A-A418-0F7045CCE44C}" name="penyiara_televisi_l"/>
-    <tableColumn id="155" xr3:uid="{99038E0D-9011-A747-83B5-47BEDDC2D8DB}" name="penyiara_televisi_p"/>
-    <tableColumn id="156" xr3:uid="{151FB6F7-DA79-0D42-BC55-AFAAF804F269}" name="penyiara_radio_l"/>
-    <tableColumn id="157" xr3:uid="{D8D83E16-B2E3-3347-A167-FA276E49E333}" name="penyiara_radio_p"/>
-    <tableColumn id="158" xr3:uid="{21AECABF-C6AD-724A-B8DF-284A82B46953}" name="pelaut_l"/>
-    <tableColumn id="159" xr3:uid="{6290290F-C729-044D-AFC4-86EBCA9C5A31}" name="pelaut_p"/>
-    <tableColumn id="160" xr3:uid="{2BFE5278-D223-2B49-8DF5-E29EADF2BB8B}" name="peneliti_l"/>
-    <tableColumn id="161" xr3:uid="{FACA5EA5-CB44-5646-B0E2-7220251278EE}" name="peneliti_p"/>
-    <tableColumn id="162" xr3:uid="{357B60FC-12AB-6B4F-BE9D-3502997A331E}" name="sopir_l"/>
-    <tableColumn id="163" xr3:uid="{ED2D041C-CB49-6843-9A31-CCD20EC056B8}" name="sopir_p"/>
-    <tableColumn id="164" xr3:uid="{E264FFCB-9AD9-6C40-8040-4DDF2A249B29}" name="pialang_l"/>
-    <tableColumn id="165" xr3:uid="{9118D4A2-2E0B-4A49-A99E-2D841BDA43FA}" name="pialang_p"/>
-    <tableColumn id="166" xr3:uid="{D132DA39-46D0-1740-9549-9EDC3D3C2109}" name="paranormal_l"/>
-    <tableColumn id="167" xr3:uid="{E119A0D9-2EA1-D94C-ACB2-86534878C557}" name="paranormal_p"/>
-    <tableColumn id="168" xr3:uid="{5DE9F497-CA5D-D64C-9337-431D93FF39C9}" name="pedagang_l"/>
-    <tableColumn id="169" xr3:uid="{D2BC5C57-FEA8-654C-8694-B3623D5BF909}" name="pedagang_p"/>
-    <tableColumn id="170" xr3:uid="{D2A6673D-3CAA-6044-8DB7-DA26ECFEE117}" name="perangkat_desa_l"/>
-    <tableColumn id="171" xr3:uid="{A779C598-6DF8-8A48-B04C-38A2996AE64B}" name="perangkat_desa_p"/>
-    <tableColumn id="172" xr3:uid="{AB0C9542-099A-BD48-ABC8-420342E17E90}" name="kepala_desa_l"/>
-    <tableColumn id="173" xr3:uid="{154C1392-69FC-FB47-ABFD-689F17422A37}" name="kepala_desa_p"/>
-    <tableColumn id="174" xr3:uid="{0A5BED51-9191-6843-8AA4-375B3AD88A59}" name="biarawan_biarawati_l"/>
-    <tableColumn id="175" xr3:uid="{5050FE4C-9DC1-0544-8EA6-2ED1C3D2EDE3}" name="biarawan_biarawati_p"/>
-    <tableColumn id="176" xr3:uid="{91E18439-C41A-C749-9DEE-9FF3BA8A2A03}" name="wiraswasta_l"/>
-    <tableColumn id="177" xr3:uid="{952719BA-69DF-CC4F-A894-148C5D2FE362}" name="wiraswasta_p"/>
-    <tableColumn id="178" xr3:uid="{6AB9B0B1-F7B3-034D-9168-2F37B4462A43}" name="anggota_lembaga_tinggi_lainnya_l"/>
-    <tableColumn id="179" xr3:uid="{95F4984F-36F1-744C-A29F-93CE58902397}" name="anggota_lembaga_tinggi_lainnya_p"/>
-    <tableColumn id="180" xr3:uid="{ACE82368-7E64-0B45-B3BD-8AFF9346AFBE}" name="artis_l"/>
-    <tableColumn id="181" xr3:uid="{F27E2900-4648-9442-A904-8B225569E891}" name="artis_p"/>
-    <tableColumn id="182" xr3:uid="{68FF066D-6F03-434F-B5C0-C0A8E3A23227}" name="atlit_l"/>
-    <tableColumn id="183" xr3:uid="{3DF2934D-E22E-1C46-8140-C14291ED05C9}" name="atlit_p"/>
-    <tableColumn id="184" xr3:uid="{5EAB7777-4857-8841-99A7-A02B11D7F9EE}" name="chef_l"/>
-    <tableColumn id="185" xr3:uid="{2D5E8398-AA97-F94E-8FEA-BED22B2E4217}" name="chef_p"/>
-    <tableColumn id="186" xr3:uid="{665CDF9B-F52D-9F4E-9BEB-74303B96D71B}" name="manajer_l"/>
-    <tableColumn id="187" xr3:uid="{A161BC8C-745A-4F40-8D6D-DDF411932380}" name="manajer_p"/>
-    <tableColumn id="188" xr3:uid="{D01234A1-D920-644E-BA98-D87B2F5EBA13}" name="tenaga_tata_usaha_l"/>
-    <tableColumn id="189" xr3:uid="{696D48D1-B52C-ED4C-AF85-877662156C8B}" name="tenaga_tata_usaha_p"/>
-    <tableColumn id="190" xr3:uid="{5305D929-B508-014A-9C1C-F0C3BCFD0762}" name="operator_l"/>
-    <tableColumn id="191" xr3:uid="{8DDCC566-91A3-874C-85E3-67928768E57A}" name="operator_p"/>
-    <tableColumn id="192" xr3:uid="{C139AC47-CA6C-0B42-BBCF-2D9583E47146}" name="pekerja_pengolahan_krajinan_l"/>
-    <tableColumn id="193" xr3:uid="{D831925F-0341-B248-A1EA-9C1A6FB51B2F}" name="pekerja_pengolahan_krajinan_p"/>
-    <tableColumn id="194" xr3:uid="{61C506F1-2B8B-FC40-82C2-C80DFDEF03CC}" name="teknisi_l"/>
-    <tableColumn id="195" xr3:uid="{509BFF65-4EF6-4340-969F-BE01BEB66216}" name="teknisi_p"/>
-    <tableColumn id="196" xr3:uid="{FF834328-DE44-CC4F-B5C8-53D15BA71EFD}" name="asisten_ahli_l"/>
-    <tableColumn id="197" xr3:uid="{60ABE242-91EE-B347-9723-BF925A0C87A4}" name="asisten_ahli_p"/>
-    <tableColumn id="198" xr3:uid="{8B63441A-95AC-C341-9C4D-969CF1B529D3}" name="pekerjaan_lainnya_l"/>
-    <tableColumn id="199" xr3:uid="{F267DC26-43C6-5D4E-872B-5AB0B74603F9}" name="pekerjaan_lainnya_p"/>
+    <tableColumn id="1" xr3:uid="{07F8713C-FA35-463F-8BEB-062C06B3754C}" name="kode_wilayah"/>
+    <tableColumn id="2" xr3:uid="{819BC640-4816-4A34-AA29-E73BBF5512BD}" name="belum_tidak_bekerja_l"/>
+    <tableColumn id="3" xr3:uid="{C1D9D654-081A-4313-AAD4-ECC88D4D8C1B}" name="belum_tidak_bekerja_p"/>
+    <tableColumn id="4" xr3:uid="{6D1101ED-FD2F-432C-A3C3-9F47899E501D}" name="mengurus_rumah_tangga_l"/>
+    <tableColumn id="5" xr3:uid="{56A3B8BF-1866-4E50-B26F-890CDBE75E0F}" name="mengurus_rumah_tangga_p"/>
+    <tableColumn id="6" xr3:uid="{24CD2EE9-86D8-4F67-A4A0-0AFE9582B934}" name="pelajar_mahasiswa_l"/>
+    <tableColumn id="7" xr3:uid="{D210E650-8A0B-4C7F-A20D-96B4EA066477}" name="pelajar_mahasiswa_p"/>
+    <tableColumn id="8" xr3:uid="{766885F8-BFF5-4B0C-BF3B-263CFFFDD381}" name="pensiunan_l"/>
+    <tableColumn id="9" xr3:uid="{EC9849B5-37DE-445A-BD7D-B7AC4F56BBAF}" name="pensiunan_p"/>
+    <tableColumn id="10" xr3:uid="{3C8C5BCF-5532-4E5D-9F27-13BD9C57A805}" name="pegawai_negeri_sipil_pns_l"/>
+    <tableColumn id="11" xr3:uid="{280B4D03-6DBE-497C-8461-E2BB06B40496}" name="pegawai_negeri_sipil_pns_p"/>
+    <tableColumn id="12" xr3:uid="{CF2C9455-26CF-490E-AE03-BD3DC9A07831}" name="tentara_nasional_indonesia_tni_l"/>
+    <tableColumn id="13" xr3:uid="{4C280ECD-E338-454B-9157-8C1CED3489CF}" name="tentara_nasional_indonesia_tni_p"/>
+    <tableColumn id="14" xr3:uid="{530CB6B3-B9D0-4F11-9CF1-41BD73F327DA}" name="kepolisian_ri_polri_l"/>
+    <tableColumn id="15" xr3:uid="{A460B32A-1FBC-4E5E-ABFB-0147A2A1308A}" name="kepolisian_ri_polri_p"/>
+    <tableColumn id="16" xr3:uid="{E4CC5F1A-51DA-4860-AD66-D7226F3AE4D7}" name="perdagangan_l"/>
+    <tableColumn id="17" xr3:uid="{6EC87A18-0B23-41FE-9D23-EB8B26D34A21}" name="perdagangan_p"/>
+    <tableColumn id="18" xr3:uid="{779A8C78-1200-40E1-8A70-E62793FF4FD4}" name="petani_pekebun_l"/>
+    <tableColumn id="19" xr3:uid="{411FC5FF-40D5-4244-AD68-E673875B3D87}" name="petani_pekebun_p"/>
+    <tableColumn id="20" xr3:uid="{E3994DC5-0C13-4718-BB02-CD99DC33CFE1}" name="peternak_l"/>
+    <tableColumn id="21" xr3:uid="{8B121A8C-9B4C-47DB-BC83-87CE82AC7842}" name="peternak_p"/>
+    <tableColumn id="22" xr3:uid="{B10EE92B-AE1A-4D76-8CB9-5FE6FB90CFE5}" name="nelayan_perikanan_l"/>
+    <tableColumn id="23" xr3:uid="{A3067F95-2C1E-4294-AFAE-889BCAE36BBC}" name="nelayan_perikanan_p"/>
+    <tableColumn id="24" xr3:uid="{6D9AF3FB-2C85-4C1C-8A1B-7F7A3893B75C}" name="industri_l"/>
+    <tableColumn id="25" xr3:uid="{60A46B83-3932-4722-AFD6-DC733CC2F40D}" name="industri_p"/>
+    <tableColumn id="26" xr3:uid="{E8C7E38A-136D-44B4-9D1A-8FAAA6B9D96E}" name="konstruksi_l"/>
+    <tableColumn id="27" xr3:uid="{1475EA8C-27D9-4A1C-BDC6-9974F2BD0F50}" name="konstruksi_p"/>
+    <tableColumn id="28" xr3:uid="{B00BEC67-02F9-4714-96D2-CE8E455FEAEC}" name="transportasi_l"/>
+    <tableColumn id="29" xr3:uid="{59BEABED-ECA9-4248-A9AD-1C128E6EB6F0}" name="transportasi_p"/>
+    <tableColumn id="30" xr3:uid="{D9B1257D-9D5A-4B99-83C0-7BE11E121A67}" name="karyawan_swasta_l"/>
+    <tableColumn id="31" xr3:uid="{3D6A1F93-DC02-49CC-A3FE-A4C0BA8AE749}" name="karyawan_swasta_p"/>
+    <tableColumn id="32" xr3:uid="{BEBDE502-955A-4EB5-BF59-EE9C86BFF442}" name="karyawan_bumn_l"/>
+    <tableColumn id="33" xr3:uid="{9997B382-7621-43BF-837D-B7D38564ADCC}" name="karyawan_bumn_p"/>
+    <tableColumn id="34" xr3:uid="{0BAD1822-4FB2-4C63-A1A5-0E5BA0863FE8}" name="karyawan_bumd_l"/>
+    <tableColumn id="35" xr3:uid="{D5B3D7B7-D647-4EBB-AF30-19FEECAEEC04}" name="karyawan_bumd_p"/>
+    <tableColumn id="36" xr3:uid="{A7889EF1-EC4E-461B-8DFB-03DC23FF758A}" name="karyawan_honorer_l"/>
+    <tableColumn id="37" xr3:uid="{2525D648-3DDA-41FC-B0DF-6AD940E4E151}" name="karyawan_honorer_p"/>
+    <tableColumn id="38" xr3:uid="{4BBDB50E-84C6-4748-A670-3CDD20FC7617}" name="buruh_harian_lepas_l"/>
+    <tableColumn id="39" xr3:uid="{4DFCFED4-CCCF-407F-B92A-F13CE52BE4C4}" name="buruh_harian_lepas_p"/>
+    <tableColumn id="40" xr3:uid="{78730A19-1DF9-4D9C-AAC2-44F3E43F2FDB}" name="buruh_tani_perkebunan_l"/>
+    <tableColumn id="41" xr3:uid="{5101EBB3-72C0-43AD-8EC6-9ACFA83CDEB3}" name="buruh_tani_perkebunan_p"/>
+    <tableColumn id="42" xr3:uid="{3FB09771-7A01-4759-8B1B-ADE4107F78C9}" name="buruh_nelayan_perikanan_l"/>
+    <tableColumn id="43" xr3:uid="{78E48065-8B00-42D6-B9E5-1BA31EDEBC64}" name="buruh_nelayan_perikanan_p"/>
+    <tableColumn id="44" xr3:uid="{A712AB07-7EC0-43BD-AF3D-2DD70167B4B0}" name="buruh_peternakan_l"/>
+    <tableColumn id="45" xr3:uid="{944A2746-B179-4D6F-AEFF-541AF47C104F}" name="buruh_peternakan_p"/>
+    <tableColumn id="46" xr3:uid="{4027583F-3A0A-4A13-8083-654C52F736BF}" name="pembantu_rumah_tangga_l"/>
+    <tableColumn id="47" xr3:uid="{E1C63FB9-1327-4877-9D7C-1B6CD905693E}" name="pembantu_rumah_tangga_p"/>
+    <tableColumn id="48" xr3:uid="{3FE1904E-D893-4FFB-A3BB-A9ABE407C074}" name="tukang_cukur_l"/>
+    <tableColumn id="49" xr3:uid="{73D394D6-550A-4E4E-9687-31840C63A9DB}" name="tukang_cukur_p"/>
+    <tableColumn id="50" xr3:uid="{C67C992C-0814-445B-961A-8CDCD608E0BC}" name="tukang_listrik_l"/>
+    <tableColumn id="51" xr3:uid="{32537DB8-C4FE-466F-B438-4D26052A1172}" name="tukang_listrik_p"/>
+    <tableColumn id="52" xr3:uid="{EA81E295-BE83-4247-89EB-FD444CB4C270}" name="tukang_batu_l"/>
+    <tableColumn id="53" xr3:uid="{D6032F94-D74D-4A50-AE6B-BB48DC8FB529}" name="tukang_batu_p"/>
+    <tableColumn id="54" xr3:uid="{91776432-8852-4A95-8BC5-E170F6F4DC93}" name="tukang_kayu_l"/>
+    <tableColumn id="55" xr3:uid="{5B9C514C-452B-492B-92A4-F95E22C8CE8D}" name="tukang_kayu_p"/>
+    <tableColumn id="56" xr3:uid="{C3685A91-308F-42F2-B206-02C18475062D}" name="tukang_sol_sepatu_l"/>
+    <tableColumn id="57" xr3:uid="{19BB7CA1-3C80-4071-8A71-C5B2EC2D4F6B}" name="tukang_sol_sepatu_p"/>
+    <tableColumn id="58" xr3:uid="{CAD28231-9461-45BB-8CFD-468346899CCD}" name="tukang_las_pandai_besi_l"/>
+    <tableColumn id="59" xr3:uid="{184D0ACC-E773-4AD6-852D-86BFCA802FA0}" name="tukang_las_pandai_besi_p"/>
+    <tableColumn id="60" xr3:uid="{F072D90B-9AD8-4B12-95A9-2D111049D646}" name="tukang_jahit_l"/>
+    <tableColumn id="61" xr3:uid="{F848A6A0-413C-49AD-9D85-23D39250F7F8}" name="tukang_jahit_p"/>
+    <tableColumn id="62" xr3:uid="{C4058AB1-CDEB-424C-969C-20494429BA61}" name="tukang_gigi_l"/>
+    <tableColumn id="63" xr3:uid="{6409871A-EF28-410B-8CA0-C729C34F98BF}" name="tukang_gigi_p"/>
+    <tableColumn id="64" xr3:uid="{B86DD2DF-F1C3-4BB4-9554-667F036E6347}" name="penata_rias_l"/>
+    <tableColumn id="65" xr3:uid="{D6885CF2-9E9F-4A44-BE66-65FEB3E58AED}" name="penata_rias_p"/>
+    <tableColumn id="66" xr3:uid="{690FCBA0-46AE-4D2B-BBCF-CDB3E4D7EDCB}" name="penata_busana_l"/>
+    <tableColumn id="67" xr3:uid="{A2373803-858F-4096-9C2E-598126C4D555}" name="penata_busana_p"/>
+    <tableColumn id="68" xr3:uid="{27EE64E6-4BE9-4CF0-A321-9976A437939C}" name="penata_rambut_l"/>
+    <tableColumn id="69" xr3:uid="{6E471127-806A-4499-943A-C6F8087BB5DC}" name="penata_rambut_p"/>
+    <tableColumn id="70" xr3:uid="{B0203376-8C49-46C3-9F23-CFFFB1F38FAD}" name="mekanik_l"/>
+    <tableColumn id="71" xr3:uid="{8BD957C2-5D07-4DC5-9B67-6248B59CB73E}" name="mekanik_p"/>
+    <tableColumn id="72" xr3:uid="{1254965E-F84A-460B-906A-1CA67CFD7DC5}" name="seniman_l"/>
+    <tableColumn id="73" xr3:uid="{92D7EA24-80F9-4D30-8D08-AC7E969A9884}" name="seniman_p"/>
+    <tableColumn id="74" xr3:uid="{C950326D-3A08-49C8-9439-45F707EB18B4}" name="tabib_l"/>
+    <tableColumn id="75" xr3:uid="{B5FD623E-1D84-4E9E-87F3-3B17A8431EC2}" name="tabib_p"/>
+    <tableColumn id="76" xr3:uid="{44E57D5E-DED1-4FD6-A9AB-A5C254E650A5}" name="paraji_l"/>
+    <tableColumn id="77" xr3:uid="{E33A8BDA-9FCB-41BB-B3E6-F4DE6B99A908}" name="paraji_p"/>
+    <tableColumn id="78" xr3:uid="{E177144E-2B75-4F0E-8DEA-E21A091D88DD}" name="perancang_busana_l"/>
+    <tableColumn id="79" xr3:uid="{43C9E89F-E372-4685-80B4-241D3E593C52}" name="perancang_busana_p"/>
+    <tableColumn id="80" xr3:uid="{238598FC-A917-4F08-BF99-97111F45329F}" name="penterjemah_l"/>
+    <tableColumn id="81" xr3:uid="{7DF25011-5FFD-42AB-A7F5-D3665C9E0EC9}" name="penterjemah_p"/>
+    <tableColumn id="82" xr3:uid="{4426D08F-63D3-4955-9A32-EEA1E84362C5}" name="imam_masjid_l"/>
+    <tableColumn id="83" xr3:uid="{E9F3C93F-75B5-4CDF-8111-00A34EA39A32}" name="imam_masjid_p"/>
+    <tableColumn id="84" xr3:uid="{888F2203-D2BC-4927-AD22-BA74ACC572FE}" name="pendeta_l"/>
+    <tableColumn id="85" xr3:uid="{653F7AB8-EED3-4EE0-A4AB-8D4EF81DBB3A}" name="pendeta_p"/>
+    <tableColumn id="86" xr3:uid="{A360AD57-A7A2-4D02-8341-69C63A296B2F}" name="pastor_l"/>
+    <tableColumn id="87" xr3:uid="{F7194232-5123-4718-A7BB-41E0807093DE}" name="pastor_p"/>
+    <tableColumn id="88" xr3:uid="{DABEE81A-6A6B-4EF2-8CF4-030DC0B26620}" name="wartawan_l"/>
+    <tableColumn id="89" xr3:uid="{47D7F7F8-CB87-4E39-912E-21A564E889EB}" name="wartawan_p"/>
+    <tableColumn id="90" xr3:uid="{3FEECE0B-4B9F-4F0A-A76E-6E3FBED5FFE5}" name="ustadz_mubaligh_l"/>
+    <tableColumn id="91" xr3:uid="{AF885BA5-2A75-4DD4-963A-73F57E3801EE}" name="ustadz_mubaligh_p"/>
+    <tableColumn id="92" xr3:uid="{717A774F-C1F4-4F7D-8666-973B4B21CF24}" name="juru_masak_l"/>
+    <tableColumn id="93" xr3:uid="{DF8A3DCB-1454-444D-8CD6-10D6B181A1F6}" name="juru_masak_p"/>
+    <tableColumn id="94" xr3:uid="{C9C06DCE-4FFE-4ED3-A0CE-7C747EC3DBE5}" name="promotor_acara_l"/>
+    <tableColumn id="95" xr3:uid="{69EB9B80-DE4B-4261-B357-CBAD44E82D7B}" name="promotor_acara_p"/>
+    <tableColumn id="96" xr3:uid="{B9ACB497-83EC-4BA0-916B-CF14E1174607}" name="anggota_dpr_ri_l"/>
+    <tableColumn id="97" xr3:uid="{CE0E2588-A109-4979-AFEE-50EACD331A9C}" name="anggota_dpr_ri_p"/>
+    <tableColumn id="98" xr3:uid="{FBE168A4-6D5F-46C1-8519-54A861D9AF97}" name="anggota_dpd_ri_l"/>
+    <tableColumn id="99" xr3:uid="{2646F626-338E-4EB1-8218-B0C11C4E6B50}" name="anggota_dpd_ri_p"/>
+    <tableColumn id="100" xr3:uid="{CEB272B4-2DEC-4B97-9350-CFF2B0DDFE73}" name="anggota_bpk_l"/>
+    <tableColumn id="101" xr3:uid="{6D5A9FD8-F2F5-4482-86C0-D28F6304ABD5}" name="anggota_bpk_p"/>
+    <tableColumn id="102" xr3:uid="{8E16A8EB-1E67-4C6C-B8CF-A899C5C18215}" name="presiden_l"/>
+    <tableColumn id="103" xr3:uid="{E92FFED4-4494-4790-A786-2DFE60471323}" name="presiden_p"/>
+    <tableColumn id="104" xr3:uid="{5FBE3B4E-08EF-4923-9B5E-986A1433E76F}" name="wakil_presiden_l"/>
+    <tableColumn id="105" xr3:uid="{233F7721-F547-4885-93CD-A6AAF63E9941}" name="wakil_presiden_p"/>
+    <tableColumn id="106" xr3:uid="{D2A63764-A6A7-4236-BC23-143BDFEFBF08}" name="anggota_mahkamah_konstitusi_l"/>
+    <tableColumn id="107" xr3:uid="{9D13BBAF-FE18-4F45-9A9F-0C7C8AA172BF}" name="anggota_mahkamah_konstitusi_p"/>
+    <tableColumn id="108" xr3:uid="{7A825738-5A54-42EF-9990-6519E99DED33}" name="anggota_kabinet_kementerian_l"/>
+    <tableColumn id="109" xr3:uid="{F43F8813-D69F-4353-9B7E-BFADEB524B4A}" name="anggota_kabinet_kementerian_p"/>
+    <tableColumn id="110" xr3:uid="{188710ED-777B-4D58-A858-E39A9C7CA051}" name="duta_besar_l"/>
+    <tableColumn id="111" xr3:uid="{41E18BB7-3186-4ABE-BDAB-8F2EAF31CDD4}" name="duta_besar _p"/>
+    <tableColumn id="112" xr3:uid="{03B93F7E-908B-43C6-9EC3-CA7C5B3E1A72}" name="gubernur_l"/>
+    <tableColumn id="113" xr3:uid="{3137BC95-98E7-497A-A0C2-E10E7452B956}" name="gubernur_p"/>
+    <tableColumn id="114" xr3:uid="{74EADB98-7A36-4227-9BC1-CB0EB0B0CABE}" name="wakil_gubernur_l"/>
+    <tableColumn id="115" xr3:uid="{B505AFCD-0319-4B5B-A45B-781A99E56A79}" name="wakil_gubernur_p"/>
+    <tableColumn id="116" xr3:uid="{2ADD1EDD-049D-46A0-9CB1-90A36C48591E}" name="bupati_l"/>
+    <tableColumn id="117" xr3:uid="{CFCF621A-5E1D-496F-B01B-9BCD6E5DF086}" name="bupati_p"/>
+    <tableColumn id="118" xr3:uid="{B9ACF6F3-847F-4EF8-80FE-7F22B1F4BC82}" name="wakil_bupati_l"/>
+    <tableColumn id="119" xr3:uid="{B8333579-81FD-4AC1-91DD-5234B8502ABA}" name="wakil_bupati_p"/>
+    <tableColumn id="120" xr3:uid="{E5FD4E1E-C511-42A7-9E67-C8FAF26BD91B}" name="walikota_l"/>
+    <tableColumn id="121" xr3:uid="{BFC60C1B-5E76-4BAC-B39D-B3AE5A26B345}" name="walikota_p"/>
+    <tableColumn id="122" xr3:uid="{7AF81612-80D5-4323-AC1F-7D1F5705878E}" name="wakil_walikota_l"/>
+    <tableColumn id="123" xr3:uid="{A22572BA-8006-44A0-B02D-48F3F97A5790}" name="wakil_walikota_p"/>
+    <tableColumn id="124" xr3:uid="{1E558961-335D-4545-8A7D-6FD7C7B20B25}" name="anggota_dprd_prop_l"/>
+    <tableColumn id="125" xr3:uid="{C67E43A1-06C1-4A51-A8C0-5EFA16859EC3}" name="anggota_dprd_prop_p"/>
+    <tableColumn id="126" xr3:uid="{F4B29A90-32AF-4053-B7A9-C2CB45CBFC86}" name="anggota_dprd_kab_kota_l"/>
+    <tableColumn id="127" xr3:uid="{7A4DA17D-6F4F-48FB-95FC-085ACE798A56}" name="anggota_dprd_kab_kota_p"/>
+    <tableColumn id="128" xr3:uid="{ADC6DCCE-68A2-4259-A5E6-C4150B6EBD24}" name="dosen_l"/>
+    <tableColumn id="129" xr3:uid="{B769E6CC-C7C5-4F59-9ACE-C5C61F15CF60}" name="dosen_p"/>
+    <tableColumn id="130" xr3:uid="{793B4C06-7895-4D19-A988-1CDA506D2276}" name="guru_l"/>
+    <tableColumn id="131" xr3:uid="{998A9347-53DB-4C5B-9367-7FEA714EE6A2}" name="guru_p"/>
+    <tableColumn id="132" xr3:uid="{26E8F22E-5D9B-4D9F-BBCA-F99EC5FADE6B}" name="pilot_l"/>
+    <tableColumn id="133" xr3:uid="{C55F7BC4-18CC-42CD-83B9-4138F7DBB033}" name="pilot_p"/>
+    <tableColumn id="134" xr3:uid="{59EEB87A-6023-413E-A6A2-FBF0587FDD8B}" name="pengacara_l"/>
+    <tableColumn id="135" xr3:uid="{5B93A4DB-C136-4041-B4BB-BB6718A0EFF6}" name="pengacara_p"/>
+    <tableColumn id="136" xr3:uid="{B46A1120-E1BA-41E6-A543-784A92BB9885}" name="notaris_l"/>
+    <tableColumn id="137" xr3:uid="{005E5274-EA02-4A14-B3F7-0DE287E891F0}" name="notaris_p"/>
+    <tableColumn id="138" xr3:uid="{57C8D1EA-7B22-4B68-AA89-A360F0F28371}" name="arsitek_l"/>
+    <tableColumn id="139" xr3:uid="{46775417-8327-4B00-8494-D0D77D2A377D}" name="arsitek_p"/>
+    <tableColumn id="140" xr3:uid="{EA33CCDA-9768-45AB-AAF4-CD30C89BC089}" name="akuntan_l"/>
+    <tableColumn id="141" xr3:uid="{6DD3ADDA-6B73-4C55-8FAF-9CBA0946E117}" name="akuntan_p"/>
+    <tableColumn id="142" xr3:uid="{D4478343-9EAE-4029-B08D-5152F3BC8C64}" name="konsultan_l"/>
+    <tableColumn id="143" xr3:uid="{97C52595-A159-4720-BA05-FE83E07A6D4A}" name="konsultan_p"/>
+    <tableColumn id="144" xr3:uid="{7519FCDE-B75A-4462-A370-03250872776D}" name="dokter_l"/>
+    <tableColumn id="145" xr3:uid="{DDB052A2-2086-4225-B080-721E5B822CB1}" name="dokter_p"/>
+    <tableColumn id="146" xr3:uid="{42941664-844A-4D96-94EB-79665717F4CB}" name="bidan_l"/>
+    <tableColumn id="147" xr3:uid="{D4FB58A7-6D4D-49AA-AE0C-850D03779469}" name="bidan_p"/>
+    <tableColumn id="148" xr3:uid="{38C31A33-58FE-49EB-962C-72835D03DC8C}" name="perawat_l"/>
+    <tableColumn id="149" xr3:uid="{FC1D3351-3C4C-43B8-AAD0-0D2D3124D6EA}" name="perawat_p"/>
+    <tableColumn id="150" xr3:uid="{7626B00C-2BC9-429C-A436-20C61C31B16F}" name="apoteker_l"/>
+    <tableColumn id="151" xr3:uid="{86EFE56F-2322-43F7-8153-7EFCBBC4FFA3}" name="apoteker_p"/>
+    <tableColumn id="152" xr3:uid="{A2BDCD92-77A4-4DDA-9F23-ABA9ECA2BE19}" name="psikiater_psikolog_l"/>
+    <tableColumn id="153" xr3:uid="{9E2B97BF-E05A-4A9E-B05C-E48F36B47727}" name="psikiater_psikolog_p"/>
+    <tableColumn id="154" xr3:uid="{5485D929-D28F-447E-95EA-112AB3929C14}" name="penyiar_televisi_l"/>
+    <tableColumn id="155" xr3:uid="{5DE79EB2-778B-4BB7-A5BC-D2E94EC1EAD4}" name="penyiar_televisi_p"/>
+    <tableColumn id="156" xr3:uid="{CABEE969-3733-4166-BE48-899A53FD81D5}" name="penyiar_radio_l"/>
+    <tableColumn id="157" xr3:uid="{408D39D7-28DE-4A66-A6E4-FEFDFC7C1595}" name="penyiar_radio_p"/>
+    <tableColumn id="158" xr3:uid="{D768C0B7-32CF-4B4C-A07F-9A188CA66526}" name="pelaut_l"/>
+    <tableColumn id="159" xr3:uid="{D0989E74-0312-415A-ABEC-5920A9F65C6E}" name="pelaut_p"/>
+    <tableColumn id="160" xr3:uid="{448A679F-D44C-425F-94FD-ADA96AF99E5C}" name="peneliti_l"/>
+    <tableColumn id="161" xr3:uid="{030883C7-980E-4C52-9F04-BE097811EFCF}" name="peneliti_p"/>
+    <tableColumn id="162" xr3:uid="{1F59B427-EE0A-41B9-8AE5-D7EC390E7AF6}" name="sopir_l"/>
+    <tableColumn id="163" xr3:uid="{4152A710-184D-425A-9DCE-A951527E8342}" name="sopir_p"/>
+    <tableColumn id="164" xr3:uid="{FF3B2ECB-BF28-4E8E-A03C-ED3B822D53D3}" name="pialang_l"/>
+    <tableColumn id="165" xr3:uid="{12EDACAE-99B5-42B7-9B7A-E7467AD311AA}" name="pialang_p"/>
+    <tableColumn id="166" xr3:uid="{BE35B466-82C6-441B-A561-C032410703F6}" name="paranormal_l"/>
+    <tableColumn id="167" xr3:uid="{F4304FE2-9D4A-4125-88AA-7140CAB9DB8F}" name="paranormal_p"/>
+    <tableColumn id="168" xr3:uid="{6B797503-2199-4214-84D2-5DBC96F4404F}" name="pedagang_l"/>
+    <tableColumn id="169" xr3:uid="{42EE2C3A-1CC7-45B4-B5FB-82FD1D383F9C}" name="pedagang_p"/>
+    <tableColumn id="170" xr3:uid="{9C410F39-CB1A-4AE7-8117-8A53A890B13E}" name="perangkat_desa_l"/>
+    <tableColumn id="171" xr3:uid="{7B608AC7-6F96-46BD-9B45-D9003EA0984A}" name="perangkat_desa_p"/>
+    <tableColumn id="172" xr3:uid="{F3F7B10C-2F38-4612-B5D3-3AF7691854BD}" name="kepala_desa_l"/>
+    <tableColumn id="173" xr3:uid="{E85DD4E0-47E9-45FE-BA0A-603C0EA097E9}" name="kepala_desa_p"/>
+    <tableColumn id="174" xr3:uid="{68693285-060C-4A30-A486-AC15A117F1AA}" name="biarawan_biarawati_l"/>
+    <tableColumn id="175" xr3:uid="{716D4494-35D4-4B8C-9FD4-4D949DCDB746}" name="biarawan_biarawati_p"/>
+    <tableColumn id="176" xr3:uid="{15357C01-7BCE-4FB1-8A7D-8A5682A08F5E}" name="wiraswasta_l"/>
+    <tableColumn id="177" xr3:uid="{1FC6213C-6BE4-4835-820E-90A0D2F3D895}" name="wiraswasta_p"/>
+    <tableColumn id="178" xr3:uid="{F289014B-3CE1-4181-92C5-015D69105CE7}" name="anggota_lembaga_tinggi_lainnya_l"/>
+    <tableColumn id="179" xr3:uid="{F5194F7D-0D7C-43FE-ACAE-190489D9B3B2}" name="anggota_lembaga_tinggi_lainnya_p"/>
+    <tableColumn id="180" xr3:uid="{49A30901-1E38-47C9-9C95-E7AB1F61B155}" name="artis_l"/>
+    <tableColumn id="181" xr3:uid="{1ADD12EF-6D69-4FB3-9B3D-1F151EA612FA}" name="artis_p"/>
+    <tableColumn id="182" xr3:uid="{70E7D0ED-0DA6-4E21-BB28-0603AF0AF6DF}" name="atlit_l"/>
+    <tableColumn id="183" xr3:uid="{620D07CE-56E8-4F6F-BFC1-976ABDC91AE8}" name="atlit_p"/>
+    <tableColumn id="184" xr3:uid="{DD5D6F28-549D-4D7F-BFEA-D48CF92C4E27}" name="chef_l"/>
+    <tableColumn id="185" xr3:uid="{0EC1998B-D523-41BD-91B4-00D4AC148FEB}" name="chef_p"/>
+    <tableColumn id="186" xr3:uid="{2A5D20D6-1FF0-44CA-A667-A320257069B6}" name="manajer_l"/>
+    <tableColumn id="187" xr3:uid="{8D72FCFF-2A0B-45ED-944C-7F422A5A4A23}" name="manajer_p"/>
+    <tableColumn id="188" xr3:uid="{8659F9BC-9C31-493C-9E67-D7FF74469082}" name="tenaga_tata_usaha_l"/>
+    <tableColumn id="189" xr3:uid="{AAA12F10-6562-4206-B83F-398EC8E04D25}" name="tenaga_tata_usaha_p"/>
+    <tableColumn id="190" xr3:uid="{1F1201F6-B21D-4EA6-ACD2-E3710E39A541}" name="operator_l"/>
+    <tableColumn id="191" xr3:uid="{579366BD-E71E-4CAE-9DCB-A897A8D2C8AE}" name="operator_p"/>
+    <tableColumn id="192" xr3:uid="{BFB1FA9F-E8B8-4C33-88D3-495CC8D47802}" name="pekerja_pengolahan_kerajinan_l"/>
+    <tableColumn id="193" xr3:uid="{2637B829-24AB-4953-8A4C-5B4592EC2B27}" name="pekerja_pengolahan_kerajinan_p"/>
+    <tableColumn id="194" xr3:uid="{40330E00-2D4F-4704-8499-0CAFB9D82396}" name="teknisi_l"/>
+    <tableColumn id="195" xr3:uid="{DC2BB7C2-17D9-4E36-9E86-55AAA8B69A1E}" name="teknisi_p"/>
+    <tableColumn id="196" xr3:uid="{0F913E52-5B5A-4509-8EF1-E07066972E44}" name="asisten_ahli_l"/>
+    <tableColumn id="197" xr3:uid="{1B504B5C-5217-4018-88A0-6E890AA22D52}" name="asisten_ahli_p"/>
+    <tableColumn id="198" xr3:uid="{D1F90DE7-004E-4872-9910-69F9B951BB7C}" name="pekerjaan_lainnya_l"/>
+    <tableColumn id="199" xr3:uid="{918E0E61-5463-4387-B136-E204C92F56F1}" name="pekerjaan_lainnya_p"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1237,179 +1209,210 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{078D12A0-4C6E-E740-89EE-DEA1F076E528}">
-  <dimension ref="A1:GQ199"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E875D3A1-355F-460E-8C1F-4F36C042A8D4}">
+  <dimension ref="A1:GQ1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.5" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="22.5" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.33203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="21.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="10" width="25.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.33203125" customWidth="1"/>
-    <col min="12" max="12" width="30.5" customWidth="1"/>
-    <col min="13" max="13" width="31" customWidth="1"/>
-    <col min="14" max="14" width="19.83203125" customWidth="1"/>
-    <col min="15" max="15" width="20.33203125" customWidth="1"/>
-    <col min="16" max="16" width="15.5" customWidth="1"/>
-    <col min="17" max="17" width="16" customWidth="1"/>
-    <col min="18" max="18" width="17.83203125" customWidth="1"/>
-    <col min="19" max="19" width="18.33203125" customWidth="1"/>
-    <col min="20" max="20" width="12.1640625" customWidth="1"/>
-    <col min="21" max="21" width="12.6640625" customWidth="1"/>
-    <col min="22" max="22" width="20.1640625" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" customWidth="1"/>
+    <col min="4" max="4" width="25.88671875" customWidth="1"/>
+    <col min="5" max="5" width="26.5546875" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" customWidth="1"/>
+    <col min="7" max="7" width="20.77734375" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="11" max="11" width="26.6640625" customWidth="1"/>
+    <col min="12" max="12" width="30.44140625" customWidth="1"/>
+    <col min="13" max="13" width="31.109375" customWidth="1"/>
+    <col min="14" max="14" width="19.44140625" customWidth="1"/>
+    <col min="15" max="15" width="20.109375" customWidth="1"/>
+    <col min="16" max="16" width="15.21875" customWidth="1"/>
+    <col min="17" max="17" width="15.88671875" customWidth="1"/>
+    <col min="18" max="18" width="17.5546875" customWidth="1"/>
+    <col min="19" max="19" width="18.21875" customWidth="1"/>
+    <col min="20" max="20" width="11.33203125" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="22" width="20" customWidth="1"/>
     <col min="23" max="23" width="20.6640625" customWidth="1"/>
-    <col min="24" max="24" width="11.1640625" customWidth="1"/>
-    <col min="25" max="25" width="11.6640625" customWidth="1"/>
-    <col min="26" max="26" width="13.6640625" customWidth="1"/>
-    <col min="27" max="27" width="14.1640625" customWidth="1"/>
-    <col min="28" max="28" width="15" customWidth="1"/>
-    <col min="29" max="29" width="15.5" customWidth="1"/>
-    <col min="30" max="30" width="19.5" customWidth="1"/>
-    <col min="31" max="31" width="20" customWidth="1"/>
-    <col min="32" max="32" width="18.1640625" customWidth="1"/>
+    <col min="24" max="24" width="10.33203125" customWidth="1"/>
+    <col min="25" max="25" width="11" customWidth="1"/>
+    <col min="26" max="26" width="12.88671875" customWidth="1"/>
+    <col min="27" max="27" width="13.5546875" customWidth="1"/>
+    <col min="28" max="28" width="14.109375" customWidth="1"/>
+    <col min="29" max="29" width="14.77734375" customWidth="1"/>
+    <col min="30" max="30" width="19.109375" customWidth="1"/>
+    <col min="31" max="31" width="19.77734375" customWidth="1"/>
+    <col min="32" max="32" width="18" customWidth="1"/>
     <col min="33" max="33" width="18.6640625" customWidth="1"/>
-    <col min="34" max="34" width="18.1640625" customWidth="1"/>
+    <col min="34" max="34" width="18" customWidth="1"/>
     <col min="35" max="35" width="18.6640625" customWidth="1"/>
-    <col min="36" max="36" width="19.83203125" customWidth="1"/>
-    <col min="37" max="37" width="20.33203125" customWidth="1"/>
-    <col min="38" max="38" width="20.83203125" customWidth="1"/>
-    <col min="39" max="39" width="21.33203125" customWidth="1"/>
-    <col min="40" max="40" width="24" customWidth="1"/>
-    <col min="41" max="41" width="24.5" customWidth="1"/>
-    <col min="42" max="42" width="25.6640625" customWidth="1"/>
-    <col min="43" max="43" width="26.1640625" customWidth="1"/>
-    <col min="44" max="44" width="19.6640625" customWidth="1"/>
-    <col min="45" max="45" width="20.1640625" customWidth="1"/>
-    <col min="46" max="46" width="25.83203125" customWidth="1"/>
-    <col min="47" max="47" width="26.33203125" customWidth="1"/>
-    <col min="48" max="48" width="16" customWidth="1"/>
-    <col min="49" max="49" width="16.5" customWidth="1"/>
-    <col min="50" max="50" width="16.1640625" customWidth="1"/>
-    <col min="51" max="51" width="16.6640625" customWidth="1"/>
-    <col min="52" max="52" width="15" customWidth="1"/>
-    <col min="53" max="53" width="15.5" customWidth="1"/>
-    <col min="54" max="54" width="15.1640625" customWidth="1"/>
-    <col min="55" max="55" width="15.6640625" customWidth="1"/>
-    <col min="56" max="56" width="20.33203125" customWidth="1"/>
-    <col min="57" max="57" width="20.83203125" customWidth="1"/>
-    <col min="58" max="58" width="24.5" customWidth="1"/>
-    <col min="59" max="59" width="25" customWidth="1"/>
-    <col min="60" max="60" width="15" customWidth="1"/>
-    <col min="61" max="61" width="15.5" customWidth="1"/>
-    <col min="62" max="62" width="14.33203125" customWidth="1"/>
-    <col min="63" max="63" width="14.83203125" customWidth="1"/>
-    <col min="64" max="64" width="14.5" customWidth="1"/>
-    <col min="65" max="65" width="15" customWidth="1"/>
-    <col min="66" max="66" width="17.33203125" customWidth="1"/>
-    <col min="67" max="67" width="17.83203125" customWidth="1"/>
-    <col min="68" max="68" width="17.33203125" customWidth="1"/>
-    <col min="69" max="69" width="17.83203125" customWidth="1"/>
-    <col min="70" max="70" width="12" customWidth="1"/>
-    <col min="71" max="71" width="12.5" customWidth="1"/>
-    <col min="72" max="72" width="12" customWidth="1"/>
-    <col min="73" max="73" width="12.5" customWidth="1"/>
+    <col min="36" max="36" width="19.88671875" customWidth="1"/>
+    <col min="37" max="37" width="20.5546875" customWidth="1"/>
+    <col min="38" max="38" width="20.88671875" customWidth="1"/>
+    <col min="39" max="39" width="21.5546875" customWidth="1"/>
+    <col min="40" max="40" width="24.33203125" customWidth="1"/>
+    <col min="41" max="41" width="25" customWidth="1"/>
+    <col min="42" max="42" width="26.109375" customWidth="1"/>
+    <col min="43" max="43" width="26.77734375" customWidth="1"/>
+    <col min="44" max="44" width="19.5546875" customWidth="1"/>
+    <col min="45" max="45" width="20.21875" customWidth="1"/>
+    <col min="46" max="46" width="25.77734375" customWidth="1"/>
+    <col min="47" max="47" width="26.44140625" customWidth="1"/>
+    <col min="48" max="48" width="15.6640625" customWidth="1"/>
+    <col min="49" max="49" width="16.33203125" customWidth="1"/>
+    <col min="50" max="50" width="15.33203125" customWidth="1"/>
+    <col min="51" max="51" width="16" customWidth="1"/>
+    <col min="52" max="52" width="14.5546875" customWidth="1"/>
+    <col min="53" max="53" width="15.21875" customWidth="1"/>
+    <col min="54" max="54" width="14.88671875" customWidth="1"/>
+    <col min="55" max="55" width="15.5546875" customWidth="1"/>
+    <col min="56" max="56" width="20.109375" customWidth="1"/>
+    <col min="57" max="57" width="20.77734375" customWidth="1"/>
+    <col min="58" max="58" width="24.5546875" customWidth="1"/>
+    <col min="59" max="59" width="25.21875" customWidth="1"/>
+    <col min="60" max="60" width="14.33203125" customWidth="1"/>
+    <col min="61" max="61" width="15" customWidth="1"/>
+    <col min="62" max="62" width="13.88671875" customWidth="1"/>
+    <col min="63" max="63" width="14.5546875" customWidth="1"/>
+    <col min="64" max="64" width="13.77734375" customWidth="1"/>
+    <col min="65" max="65" width="14.44140625" customWidth="1"/>
+    <col min="66" max="66" width="17" customWidth="1"/>
+    <col min="67" max="67" width="17.6640625" customWidth="1"/>
+    <col min="68" max="68" width="16.6640625" customWidth="1"/>
+    <col min="69" max="69" width="17.33203125" customWidth="1"/>
+    <col min="70" max="70" width="11" customWidth="1"/>
+    <col min="71" max="71" width="11.6640625" customWidth="1"/>
+    <col min="72" max="72" width="11.109375" customWidth="1"/>
+    <col min="73" max="73" width="11.77734375" customWidth="1"/>
+    <col min="74" max="74" width="8.109375" customWidth="1"/>
+    <col min="75" max="75" width="8.77734375" customWidth="1"/>
+    <col min="76" max="76" width="8.5546875" customWidth="1"/>
+    <col min="77" max="77" width="9.21875" customWidth="1"/>
     <col min="78" max="78" width="20.33203125" customWidth="1"/>
-    <col min="79" max="79" width="20.83203125" customWidth="1"/>
-    <col min="80" max="80" width="15.33203125" customWidth="1"/>
-    <col min="81" max="81" width="15.83203125" customWidth="1"/>
-    <col min="82" max="82" width="16.1640625" customWidth="1"/>
-    <col min="83" max="83" width="16.6640625" customWidth="1"/>
-    <col min="84" max="84" width="11.5" customWidth="1"/>
-    <col min="85" max="85" width="12" customWidth="1"/>
-    <col min="88" max="88" width="12.83203125" customWidth="1"/>
-    <col min="89" max="89" width="13.33203125" customWidth="1"/>
-    <col min="90" max="90" width="18.83203125" customWidth="1"/>
-    <col min="91" max="91" width="19.33203125" customWidth="1"/>
-    <col min="92" max="92" width="14.5" customWidth="1"/>
-    <col min="93" max="93" width="15" customWidth="1"/>
-    <col min="94" max="94" width="18" customWidth="1"/>
-    <col min="95" max="95" width="18.5" customWidth="1"/>
-    <col min="96" max="96" width="17" customWidth="1"/>
-    <col min="97" max="97" width="17.5" customWidth="1"/>
+    <col min="79" max="79" width="21" customWidth="1"/>
+    <col min="80" max="80" width="14.44140625" customWidth="1"/>
+    <col min="81" max="81" width="15.109375" customWidth="1"/>
+    <col min="82" max="82" width="15" customWidth="1"/>
+    <col min="83" max="83" width="15.6640625" customWidth="1"/>
+    <col min="84" max="84" width="10.77734375" customWidth="1"/>
+    <col min="85" max="85" width="11.44140625" customWidth="1"/>
+    <col min="86" max="86" width="9.33203125" customWidth="1"/>
+    <col min="87" max="87" width="10" customWidth="1"/>
+    <col min="88" max="88" width="12.109375" customWidth="1"/>
+    <col min="89" max="89" width="12.77734375" customWidth="1"/>
+    <col min="90" max="90" width="18.5546875" customWidth="1"/>
+    <col min="91" max="91" width="19.21875" customWidth="1"/>
+    <col min="92" max="92" width="13.77734375" customWidth="1"/>
+    <col min="93" max="93" width="14.44140625" customWidth="1"/>
+    <col min="94" max="94" width="17.44140625" customWidth="1"/>
+    <col min="95" max="95" width="18.109375" customWidth="1"/>
+    <col min="96" max="96" width="16.88671875" customWidth="1"/>
+    <col min="97" max="97" width="17.5546875" customWidth="1"/>
     <col min="98" max="98" width="17.33203125" customWidth="1"/>
-    <col min="99" max="99" width="17.83203125" customWidth="1"/>
-    <col min="100" max="100" width="15.33203125" customWidth="1"/>
-    <col min="101" max="101" width="15.83203125" customWidth="1"/>
-    <col min="102" max="102" width="12" customWidth="1"/>
-    <col min="103" max="103" width="12.5" customWidth="1"/>
-    <col min="104" max="104" width="17.1640625" customWidth="1"/>
-    <col min="105" max="105" width="17.6640625" customWidth="1"/>
-    <col min="106" max="106" width="30.83203125" customWidth="1"/>
-    <col min="107" max="107" width="31.33203125" customWidth="1"/>
-    <col min="108" max="108" width="29.83203125" customWidth="1"/>
-    <col min="109" max="109" width="30.33203125" customWidth="1"/>
-    <col min="110" max="110" width="14" customWidth="1"/>
-    <col min="111" max="111" width="14.83203125" customWidth="1"/>
-    <col min="112" max="112" width="12.1640625" customWidth="1"/>
-    <col min="113" max="113" width="12.6640625" customWidth="1"/>
-    <col min="114" max="114" width="17.33203125" customWidth="1"/>
-    <col min="115" max="115" width="17.83203125" customWidth="1"/>
-    <col min="118" max="118" width="15.1640625" customWidth="1"/>
-    <col min="119" max="119" width="15.6640625" customWidth="1"/>
-    <col min="120" max="120" width="11.83203125" customWidth="1"/>
-    <col min="121" max="121" width="12.33203125" customWidth="1"/>
-    <col min="122" max="122" width="17" customWidth="1"/>
-    <col min="123" max="123" width="17.5" customWidth="1"/>
-    <col min="124" max="124" width="20.5" customWidth="1"/>
-    <col min="125" max="125" width="21" customWidth="1"/>
-    <col min="126" max="126" width="24.33203125" customWidth="1"/>
-    <col min="127" max="127" width="24.83203125" customWidth="1"/>
-    <col min="134" max="134" width="13.5" customWidth="1"/>
-    <col min="135" max="135" width="14" customWidth="1"/>
-    <col min="137" max="137" width="11.1640625" customWidth="1"/>
-    <col min="139" max="139" width="11.1640625" customWidth="1"/>
-    <col min="140" max="140" width="11.5" customWidth="1"/>
-    <col min="141" max="141" width="12" customWidth="1"/>
-    <col min="142" max="142" width="13" customWidth="1"/>
-    <col min="143" max="143" width="13.5" customWidth="1"/>
-    <col min="148" max="148" width="11.5" customWidth="1"/>
-    <col min="149" max="149" width="12" customWidth="1"/>
-    <col min="151" max="151" width="11" customWidth="1"/>
-    <col min="152" max="152" width="20" customWidth="1"/>
-    <col min="153" max="153" width="20.5" customWidth="1"/>
-    <col min="154" max="154" width="18.6640625" customWidth="1"/>
-    <col min="155" max="155" width="19.1640625" customWidth="1"/>
-    <col min="156" max="156" width="16.83203125" customWidth="1"/>
-    <col min="157" max="157" width="17.33203125" customWidth="1"/>
-    <col min="160" max="160" width="11" customWidth="1"/>
-    <col min="161" max="161" width="11.5" customWidth="1"/>
-    <col min="165" max="165" width="11.33203125" customWidth="1"/>
-    <col min="166" max="166" width="14.33203125" customWidth="1"/>
-    <col min="167" max="167" width="14.83203125" customWidth="1"/>
-    <col min="168" max="168" width="12.83203125" customWidth="1"/>
-    <col min="169" max="169" width="13.33203125" customWidth="1"/>
-    <col min="170" max="170" width="18" customWidth="1"/>
-    <col min="171" max="171" width="18.5" customWidth="1"/>
-    <col min="172" max="172" width="15.1640625" customWidth="1"/>
-    <col min="173" max="173" width="15.6640625" customWidth="1"/>
-    <col min="174" max="174" width="20.83203125" customWidth="1"/>
-    <col min="175" max="175" width="21.33203125" customWidth="1"/>
-    <col min="176" max="176" width="14.33203125" customWidth="1"/>
-    <col min="177" max="177" width="14.83203125" customWidth="1"/>
-    <col min="178" max="178" width="31.6640625" customWidth="1"/>
-    <col min="179" max="179" width="32.1640625" customWidth="1"/>
-    <col min="186" max="186" width="11.6640625" customWidth="1"/>
-    <col min="187" max="187" width="12.1640625" customWidth="1"/>
-    <col min="188" max="188" width="20.5" customWidth="1"/>
-    <col min="189" max="189" width="21" customWidth="1"/>
-    <col min="190" max="190" width="11.83203125" customWidth="1"/>
-    <col min="191" max="191" width="12.33203125" customWidth="1"/>
-    <col min="192" max="192" width="28.83203125" customWidth="1"/>
-    <col min="193" max="193" width="29.33203125" customWidth="1"/>
-    <col min="195" max="195" width="11" customWidth="1"/>
-    <col min="196" max="196" width="14.83203125" customWidth="1"/>
-    <col min="197" max="197" width="15.33203125" customWidth="1"/>
-    <col min="198" max="198" width="19.6640625" customWidth="1"/>
-    <col min="199" max="199" width="20.1640625" customWidth="1"/>
+    <col min="99" max="99" width="18" customWidth="1"/>
+    <col min="100" max="100" width="15.109375" customWidth="1"/>
+    <col min="101" max="101" width="15.77734375" customWidth="1"/>
+    <col min="102" max="102" width="11.33203125" customWidth="1"/>
+    <col min="103" max="103" width="12" customWidth="1"/>
+    <col min="104" max="104" width="16.6640625" customWidth="1"/>
+    <col min="105" max="105" width="17.33203125" customWidth="1"/>
+    <col min="106" max="106" width="30.5546875" customWidth="1"/>
+    <col min="107" max="107" width="31.21875" customWidth="1"/>
+    <col min="108" max="108" width="29.5546875" customWidth="1"/>
+    <col min="109" max="109" width="30.21875" customWidth="1"/>
+    <col min="110" max="110" width="13.44140625" customWidth="1"/>
+    <col min="111" max="111" width="14.5546875" customWidth="1"/>
+    <col min="112" max="112" width="11.77734375" customWidth="1"/>
+    <col min="113" max="113" width="12.44140625" customWidth="1"/>
+    <col min="114" max="114" width="17.109375" customWidth="1"/>
+    <col min="115" max="115" width="17.77734375" customWidth="1"/>
+    <col min="116" max="116" width="9.21875" customWidth="1"/>
+    <col min="117" max="117" width="9.88671875" customWidth="1"/>
+    <col min="118" max="118" width="14.5546875" customWidth="1"/>
+    <col min="119" max="119" width="15.21875" customWidth="1"/>
+    <col min="120" max="120" width="10.88671875" customWidth="1"/>
+    <col min="121" max="121" width="11.5546875" customWidth="1"/>
+    <col min="122" max="122" width="16.21875" customWidth="1"/>
+    <col min="123" max="123" width="16.88671875" customWidth="1"/>
+    <col min="124" max="124" width="20.88671875" customWidth="1"/>
+    <col min="125" max="125" width="21.5546875" customWidth="1"/>
+    <col min="126" max="126" width="24.6640625" customWidth="1"/>
+    <col min="127" max="127" width="25.33203125" customWidth="1"/>
+    <col min="128" max="128" width="9.21875" customWidth="1"/>
+    <col min="129" max="129" width="9.88671875" customWidth="1"/>
+    <col min="130" max="130" width="7.88671875" customWidth="1"/>
+    <col min="131" max="131" width="8.5546875" customWidth="1"/>
+    <col min="132" max="132" width="7.5546875" customWidth="1"/>
+    <col min="133" max="133" width="8.21875" customWidth="1"/>
+    <col min="134" max="134" width="12.88671875" customWidth="1"/>
+    <col min="135" max="135" width="13.5546875" customWidth="1"/>
+    <col min="136" max="136" width="9.77734375" customWidth="1"/>
+    <col min="137" max="137" width="10.44140625" customWidth="1"/>
+    <col min="138" max="138" width="9.5546875" customWidth="1"/>
+    <col min="139" max="139" width="10.21875" customWidth="1"/>
+    <col min="140" max="140" width="10.77734375" customWidth="1"/>
+    <col min="141" max="141" width="11.44140625" customWidth="1"/>
+    <col min="142" max="142" width="12.33203125" customWidth="1"/>
+    <col min="143" max="143" width="13" customWidth="1"/>
+    <col min="144" max="144" width="9.33203125" customWidth="1"/>
+    <col min="145" max="145" width="10" customWidth="1"/>
+    <col min="146" max="146" width="8.6640625" customWidth="1"/>
+    <col min="147" max="147" width="9.33203125" customWidth="1"/>
+    <col min="148" max="148" width="10.6640625" customWidth="1"/>
+    <col min="149" max="150" width="11.33203125" customWidth="1"/>
+    <col min="151" max="151" width="12" customWidth="1"/>
+    <col min="152" max="152" width="19.44140625" customWidth="1"/>
+    <col min="153" max="153" width="20.109375" customWidth="1"/>
+    <col min="154" max="154" width="17.109375" customWidth="1"/>
+    <col min="155" max="155" width="17.77734375" customWidth="1"/>
+    <col min="156" max="156" width="15.5546875" customWidth="1"/>
+    <col min="157" max="157" width="16.21875" customWidth="1"/>
+    <col min="158" max="158" width="9.109375" customWidth="1"/>
+    <col min="159" max="159" width="9.77734375" customWidth="1"/>
+    <col min="160" max="160" width="10" customWidth="1"/>
+    <col min="161" max="161" width="10.6640625" customWidth="1"/>
+    <col min="162" max="162" width="8.21875" customWidth="1"/>
+    <col min="163" max="163" width="8.88671875" customWidth="1"/>
+    <col min="164" max="164" width="10.109375" customWidth="1"/>
+    <col min="165" max="165" width="10.77734375" customWidth="1"/>
+    <col min="166" max="166" width="13.5546875" customWidth="1"/>
+    <col min="167" max="167" width="14.21875" customWidth="1"/>
+    <col min="168" max="168" width="12.44140625" customWidth="1"/>
+    <col min="169" max="169" width="13.109375" customWidth="1"/>
+    <col min="170" max="170" width="17.5546875" customWidth="1"/>
+    <col min="171" max="171" width="18.21875" customWidth="1"/>
+    <col min="172" max="172" width="14.5546875" customWidth="1"/>
+    <col min="173" max="173" width="15.21875" customWidth="1"/>
+    <col min="174" max="174" width="20.33203125" customWidth="1"/>
+    <col min="175" max="175" width="21" customWidth="1"/>
+    <col min="176" max="176" width="13.44140625" customWidth="1"/>
+    <col min="177" max="177" width="14.109375" customWidth="1"/>
+    <col min="178" max="178" width="32" customWidth="1"/>
+    <col min="179" max="179" width="32.6640625" customWidth="1"/>
+    <col min="180" max="180" width="7.5546875" customWidth="1"/>
+    <col min="181" max="181" width="8.21875" customWidth="1"/>
+    <col min="182" max="182" width="6.88671875" customWidth="1"/>
+    <col min="183" max="184" width="7.5546875" customWidth="1"/>
+    <col min="185" max="185" width="8.21875" customWidth="1"/>
+    <col min="186" max="186" width="10.6640625" customWidth="1"/>
+    <col min="187" max="187" width="11.33203125" customWidth="1"/>
+    <col min="188" max="188" width="20" customWidth="1"/>
+    <col min="189" max="189" width="20.6640625" customWidth="1"/>
+    <col min="190" max="190" width="11.109375" customWidth="1"/>
+    <col min="191" max="191" width="11.77734375" customWidth="1"/>
+    <col min="192" max="192" width="30" customWidth="1"/>
+    <col min="193" max="193" width="30.6640625" customWidth="1"/>
+    <col min="194" max="194" width="9.44140625" customWidth="1"/>
+    <col min="195" max="195" width="10.109375" customWidth="1"/>
+    <col min="196" max="196" width="14" customWidth="1"/>
+    <col min="197" max="197" width="14.6640625" customWidth="1"/>
+    <col min="198" max="198" width="19.33203125" customWidth="1"/>
+    <col min="199" max="199" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:199">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1858,749 +1861,155 @@
         <v>148</v>
       </c>
       <c r="ET1" t="s">
+        <v>191</v>
+      </c>
+      <c r="EU1" t="s">
+        <v>192</v>
+      </c>
+      <c r="EV1" t="s">
         <v>149</v>
       </c>
-      <c r="EU1" t="s">
+      <c r="EW1" t="s">
         <v>150</v>
       </c>
-      <c r="EV1" t="s">
+      <c r="EX1" t="s">
+        <v>193</v>
+      </c>
+      <c r="EY1" t="s">
+        <v>194</v>
+      </c>
+      <c r="EZ1" t="s">
+        <v>195</v>
+      </c>
+      <c r="FA1" t="s">
+        <v>196</v>
+      </c>
+      <c r="FB1" t="s">
         <v>151</v>
       </c>
-      <c r="EW1" t="s">
+      <c r="FC1" t="s">
         <v>152</v>
       </c>
-      <c r="EX1" t="s">
+      <c r="FD1" t="s">
         <v>153</v>
       </c>
-      <c r="EY1" t="s">
+      <c r="FE1" t="s">
         <v>154</v>
       </c>
-      <c r="EZ1" t="s">
+      <c r="FF1" t="s">
         <v>155</v>
       </c>
-      <c r="FA1" t="s">
+      <c r="FG1" t="s">
         <v>156</v>
       </c>
-      <c r="FB1" t="s">
+      <c r="FH1" t="s">
         <v>157</v>
       </c>
-      <c r="FC1" t="s">
+      <c r="FI1" t="s">
         <v>158</v>
       </c>
-      <c r="FD1" t="s">
+      <c r="FJ1" t="s">
         <v>159</v>
       </c>
-      <c r="FE1" t="s">
+      <c r="FK1" t="s">
         <v>160</v>
       </c>
-      <c r="FF1" t="s">
+      <c r="FL1" t="s">
         <v>161</v>
       </c>
-      <c r="FG1" t="s">
+      <c r="FM1" t="s">
         <v>162</v>
       </c>
-      <c r="FH1" t="s">
+      <c r="FN1" t="s">
         <v>163</v>
       </c>
-      <c r="FI1" t="s">
+      <c r="FO1" t="s">
         <v>164</v>
       </c>
-      <c r="FJ1" t="s">
+      <c r="FP1" t="s">
         <v>165</v>
       </c>
-      <c r="FK1" t="s">
+      <c r="FQ1" t="s">
         <v>166</v>
       </c>
-      <c r="FL1" t="s">
+      <c r="FR1" t="s">
         <v>167</v>
       </c>
-      <c r="FM1" t="s">
+      <c r="FS1" t="s">
         <v>168</v>
       </c>
-      <c r="FN1" t="s">
+      <c r="FT1" t="s">
         <v>169</v>
       </c>
-      <c r="FO1" t="s">
+      <c r="FU1" t="s">
         <v>170</v>
       </c>
-      <c r="FP1" t="s">
+      <c r="FV1" t="s">
         <v>171</v>
       </c>
-      <c r="FQ1" t="s">
+      <c r="FW1" t="s">
         <v>172</v>
       </c>
-      <c r="FR1" t="s">
+      <c r="FX1" t="s">
         <v>173</v>
       </c>
-      <c r="FS1" t="s">
+      <c r="FY1" t="s">
         <v>174</v>
       </c>
-      <c r="FT1" t="s">
+      <c r="FZ1" t="s">
         <v>175</v>
       </c>
-      <c r="FU1" t="s">
+      <c r="GA1" t="s">
         <v>176</v>
       </c>
-      <c r="FV1" t="s">
+      <c r="GB1" t="s">
         <v>177</v>
       </c>
-      <c r="FW1" t="s">
+      <c r="GC1" t="s">
         <v>178</v>
       </c>
-      <c r="FX1" t="s">
+      <c r="GD1" t="s">
         <v>179</v>
       </c>
-      <c r="FY1" t="s">
+      <c r="GE1" t="s">
         <v>180</v>
       </c>
-      <c r="FZ1" t="s">
+      <c r="GF1" t="s">
         <v>181</v>
       </c>
-      <c r="GA1" t="s">
+      <c r="GG1" t="s">
         <v>182</v>
       </c>
-      <c r="GB1" t="s">
+      <c r="GH1" t="s">
         <v>183</v>
       </c>
-      <c r="GC1" t="s">
+      <c r="GI1" t="s">
         <v>184</v>
       </c>
-      <c r="GD1" t="s">
+      <c r="GJ1" t="s">
+        <v>197</v>
+      </c>
+      <c r="GK1" t="s">
+        <v>198</v>
+      </c>
+      <c r="GL1" t="s">
         <v>185</v>
       </c>
-      <c r="GE1" t="s">
+      <c r="GM1" t="s">
         <v>186</v>
       </c>
-      <c r="GF1" t="s">
+      <c r="GN1" t="s">
         <v>187</v>
       </c>
-      <c r="GG1" t="s">
+      <c r="GO1" t="s">
         <v>188</v>
       </c>
-      <c r="GH1" t="s">
+      <c r="GP1" t="s">
         <v>189</v>
       </c>
-      <c r="GI1" t="s">
+      <c r="GQ1" t="s">
         <v>190</v>
       </c>
-      <c r="GJ1" t="s">
-        <v>191</v>
-      </c>
-      <c r="GK1" t="s">
-        <v>192</v>
-      </c>
-      <c r="GL1" t="s">
-        <v>193</v>
-      </c>
-      <c r="GM1" t="s">
-        <v>194</v>
-      </c>
-      <c r="GN1" t="s">
-        <v>195</v>
-      </c>
-      <c r="GO1" t="s">
-        <v>196</v>
-      </c>
-      <c r="GP1" t="s">
-        <v>197</v>
-      </c>
-      <c r="GQ1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="2" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-    </row>
-    <row r="3" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-    </row>
-    <row r="4" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-    </row>
-    <row r="5" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="6" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-    </row>
-    <row r="8" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-    </row>
-    <row r="9" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-    </row>
-    <row r="10" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-    </row>
-    <row r="11" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-    </row>
-    <row r="12" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
-    </row>
-    <row r="14" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-    </row>
-    <row r="15" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-    </row>
-    <row r="16" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="1"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" s="1"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" s="1"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" s="1"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="1"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="1"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" s="1"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" s="1"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" s="1"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" s="1"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" s="1"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" s="1"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" s="1"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" s="1"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" s="1"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" s="1"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" s="1"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" s="1"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" s="1"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" s="1"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" s="1"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" s="1"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" s="1"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" s="1"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" s="1"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" s="1"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" s="1"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" s="1"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" s="1"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" s="1"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" s="1"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" s="1"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63" s="1"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64" s="1"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" s="1"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" s="1"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" s="1"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" s="1"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" s="1"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" s="1"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" s="1"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A72" s="1"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A73" s="1"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A74" s="1"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A75" s="1"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A76" s="1"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A77" s="1"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A78" s="1"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A79" s="1"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A80" s="1"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A81" s="1"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A82" s="1"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A83" s="1"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A84" s="1"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A85" s="1"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A86" s="1"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A87" s="1"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A88" s="1"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A89" s="1"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A90" s="1"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A91" s="1"/>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A92" s="1"/>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A93" s="1"/>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A94" s="1"/>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A95" s="1"/>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A96" s="1"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A97" s="1"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A98" s="1"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A99" s="1"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A100" s="1"/>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A101" s="1"/>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A102" s="1"/>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A103" s="1"/>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A104" s="1"/>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A105" s="1"/>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A106" s="1"/>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A107" s="1"/>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A108" s="1"/>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A109" s="1"/>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A110" s="1"/>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A111" s="1"/>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A112" s="1"/>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A113" s="1"/>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A114" s="1"/>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A115" s="1"/>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A116" s="1"/>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A117" s="1"/>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A119" s="1"/>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A120" s="1"/>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A121" s="1"/>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A122" s="1"/>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A123" s="1"/>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A124" s="1"/>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A125" s="1"/>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A126" s="1"/>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A127" s="1"/>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A128" s="1"/>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A129" s="1"/>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A130" s="1"/>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A131" s="1"/>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A132" s="1"/>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A133" s="1"/>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A134" s="1"/>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A135" s="1"/>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A136" s="1"/>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A137" s="1"/>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A138" s="1"/>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A139" s="1"/>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A140" s="1"/>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A141" s="1"/>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A142" s="1"/>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A143" s="1"/>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A144" s="1"/>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A145" s="1"/>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A146" s="1"/>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A147" s="1"/>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A148" s="1"/>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A149" s="1"/>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A150" s="1"/>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A151" s="1"/>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A152" s="1"/>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A153" s="1"/>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A154" s="1"/>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A155" s="1"/>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A156" s="1"/>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A157" s="1"/>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A158" s="1"/>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A159" s="1"/>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A160" s="1"/>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A161" s="1"/>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A162" s="1"/>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A163" s="1"/>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A164" s="1"/>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A165" s="1"/>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A166" s="1"/>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A167" s="1"/>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A168" s="1"/>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A169" s="1"/>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A170" s="1"/>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A171" s="1"/>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A172" s="1"/>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A173" s="1"/>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A174" s="1"/>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A175" s="1"/>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A176" s="1"/>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A177" s="1"/>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A178" s="1"/>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A179" s="1"/>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A180" s="1"/>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A181" s="1"/>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A182" s="1"/>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A183" s="1"/>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A184" s="1"/>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A185" s="1"/>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A186" s="1"/>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A187" s="1"/>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A188" s="1"/>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A189" s="1"/>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A190" s="1"/>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A191" s="1"/>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A192" s="1"/>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A193" s="1"/>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A194" s="1"/>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A195" s="1"/>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A196" s="1"/>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A197" s="1"/>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A198" s="1"/>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A199" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
